--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="497">
   <si>
     <t>Filename</t>
   </si>
@@ -808,709 +808,703 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9779,0.0029,0.0093,0.0009</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.9225,0.0004,0.0015,0.0511</t>
-  </si>
-  <si>
-    <t>0.1420,0.0051,0.0000,0.8749</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9786,0.0024,0.0074,0.0015</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9496,0.0003,0.0011,0.0377</t>
+  </si>
+  <si>
+    <t>0.9560,0.0005,0.0004,0.0152</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0009,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9839,0.0006,0.0102,0.0002</t>
+  </si>
+  <si>
+    <t>0.0047,0.0005,0.9959,0.0002</t>
+  </si>
+  <si>
+    <t>0.1938,0.0014,0.8671,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0002,0.9975,0.0003</t>
+  </si>
+  <si>
+    <t>0.9653,0.0027,0.0213,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.9967,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0385,0.9672,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.9979,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.6587,0.0002,0.4248,0.0005</t>
+  </si>
+  <si>
+    <t>0.0113,0.0013,0.9821,0.0009</t>
+  </si>
+  <si>
+    <t>0.0014,0.0002,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9978,0.0008</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9992,0.0003</t>
+  </si>
+  <si>
+    <t>0.0198,0.0000,0.9833,0.0005</t>
+  </si>
+  <si>
+    <t>0.5053,0.4199,0.0079,0.0014</t>
+  </si>
+  <si>
+    <t>0.3496,0.4768,0.0380,0.0013</t>
+  </si>
+  <si>
+    <t>0.0010,0.0097,0.9981,0.0053</t>
+  </si>
+  <si>
+    <t>0.0083,0.7009,0.5622,0.0004</t>
+  </si>
+  <si>
+    <t>0.8645,0.1476,0.0015,0.0016</t>
+  </si>
+  <si>
+    <t>0.7707,0.0061,0.1634,0.0010</t>
+  </si>
+  <si>
+    <t>0.4282,0.5574,0.0080,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9553,0.7374,0.0002</t>
+  </si>
+  <si>
+    <t>0.0080,0.5946,0.3300,0.0090</t>
+  </si>
+  <si>
+    <t>0.0637,0.0009,0.9172,0.0030</t>
+  </si>
+  <si>
+    <t>0.0724,0.0031,0.9134,0.0006</t>
+  </si>
+  <si>
+    <t>0.0033,0.0001,0.9958,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.3797,0.9814,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9968,0.0039,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.2279,0.0001,0.9948</t>
+  </si>
+  <si>
+    <t>0.0004,0.9949,0.0006,0.0094</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0065,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0026,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.0003,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0019,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0010,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9891,0.0107,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0044,0.9996,0.0010</t>
+  </si>
+  <si>
+    <t>0.9980,0.0023,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9322,0.1045,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9811,0.9808,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0014,0.9985,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0003,0.9977,0.0015</t>
+  </si>
+  <si>
+    <t>0.0000,0.9772,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9993,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0435,0.0009,0.9710,0.0004</t>
+  </si>
+  <si>
+    <t>0.9882,0.0006,0.0112,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.9999,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.8928,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9826,0.9952,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.0258,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.9900,0.0000</t>
+  </si>
+  <si>
+    <t>0.0046,0.0000,0.0018,0.9972</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0044,0.0003,0.0045,0.9955</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.9975,0.1425,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9815,0.9510,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.7692,0.9689,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.4767,0.9699,0.0013</t>
+  </si>
+  <si>
+    <t>0.0000,0.9267,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9839,0.9702,0.0000</t>
+  </si>
+  <si>
+    <t>0.9940,0.0054,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
     <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0022,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0031,0.9973,0.0005</t>
+  </si>
+  <si>
+    <t>0.9622,0.0007,0.0140,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9992,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.9971,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0040,0.9931,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0327,0.9720,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.3614,0.0491,0.3191,0.0046</t>
+  </si>
+  <si>
+    <t>0.6557,0.0006,0.3709,0.0012</t>
+  </si>
+  <si>
+    <t>0.5744,0.1010,0.0740,0.0028</t>
+  </si>
+  <si>
+    <t>0.7914,0.0335,0.0309,0.0084</t>
+  </si>
+  <si>
+    <t>0.0048,0.0136,0.0209,0.9812</t>
+  </si>
+  <si>
+    <t>0.0006,0.9981,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0088</t>
+  </si>
+  <si>
+    <t>0.0000,0.9958,0.9800,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9986,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.1413,0.8339,0.0080,0.0000</t>
+  </si>
+  <si>
+    <t>0.0848,0.8923,0.0121,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0009,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0012,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0008,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.6153,0.9892,0.0009</t>
+  </si>
+  <si>
+    <t>0.0054,0.0533,0.9884,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0027,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.0016,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.9408,0.0005,0.0525,0.0007</t>
+  </si>
+  <si>
+    <t>0.3088,0.0028,0.7058,0.0009</t>
+  </si>
+  <si>
+    <t>0.0076,0.0002,0.9908,0.0004</t>
+  </si>
+  <si>
+    <t>0.4709,0.0014,0.5844,0.0008</t>
+  </si>
+  <si>
+    <t>0.0034,0.0004,0.0000,0.9990</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0017,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.9942,0.5622,0.0001</t>
+  </si>
+  <si>
+    <t>0.0410,0.9558,0.0002,0.0023</t>
+  </si>
+  <si>
+    <t>0.9972,0.0010,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.8653,0.2152,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0243,0.0004,0.0122,0.9804</t>
+  </si>
+  <si>
+    <t>0.0008,0.0029,0.9976,0.0021</t>
+  </si>
+  <si>
+    <t>0.9804,0.0006,0.0082,0.0036</t>
+  </si>
+  <si>
+    <t>0.9964,0.0006,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.0366,0.8910,0.0358,0.0018</t>
+  </si>
+  <si>
+    <t>0.9488,0.0235,0.0099,0.0021</t>
+  </si>
+  <si>
+    <t>0.9455,0.0043,0.0331,0.0009</t>
+  </si>
+  <si>
+    <t>0.2971,0.6060,0.0126,0.0033</t>
+  </si>
+  <si>
+    <t>0.9913,0.0009,0.0044,0.0002</t>
+  </si>
+  <si>
+    <t>0.7513,0.1585,0.0185,0.0036</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9953,0.0025,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9085,0.0985,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.2670,0.7824,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.5197,0.5674,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.6636,0.0109,0.3423,0.0003</t>
+  </si>
+  <si>
+    <t>0.9933,0.0066,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9853,0.0144,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9738,0.0093,0.0081,0.0011</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0206,0.9952,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.4293,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0010,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0165,0.0001,0.9936,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0159,0.0060,0.9735,0.0012</t>
+  </si>
+  <si>
+    <t>0.0005,0.0006,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0175,0.0058,0.9715,0.0008</t>
+  </si>
+  <si>
+    <t>0.0214,0.0017,0.9792,0.0001</t>
+  </si>
+  <si>
+    <t>0.0264,0.0036,0.9725,0.0001</t>
+  </si>
+  <si>
+    <t>0.0531,0.0022,0.9438,0.0009</t>
+  </si>
+  <si>
+    <t>0.3017,0.0106,0.5666,0.0060</t>
+  </si>
+  <si>
+    <t>0.0312,0.0036,0.9656,0.0013</t>
+  </si>
+  <si>
+    <t>0.0940,0.9105,0.0041,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.9980,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1158,0.9192,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.8052,0.3287,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0295,0.9756,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9259,0.0233,0.0129,0.0009</t>
+  </si>
+  <si>
+    <t>0.9870,0.0004,0.0085,0.0002</t>
+  </si>
+  <si>
+    <t>0.8824,0.0039,0.0437,0.0085</t>
+  </si>
+  <si>
+    <t>0.3031,0.0118,0.6187,0.0037</t>
+  </si>
+  <si>
+    <t>0.1595,0.0158,0.8129,0.0053</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9993,0.0026</t>
+  </si>
+  <si>
+    <t>0.0018,0.0734,0.9855,0.0017</t>
+  </si>
+  <si>
+    <t>0.0017,0.0061,0.9942,0.0005</t>
+  </si>
+  <si>
+    <t>0.0036,0.0006,0.9901,0.0036</t>
+  </si>
+  <si>
+    <t>0.0004,0.0115,0.9976,0.0005</t>
+  </si>
+  <si>
     <t>0.9994,0.0002,0.0000,0.0001</t>
   </si>
   <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9958,0.0028,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0029,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0034,0.9987,0.0015</t>
+  </si>
+  <si>
+    <t>0.0035,0.0129,0.9922,0.0009</t>
+  </si>
+  <si>
+    <t>0.6683,0.0022,0.3358,0.0035</t>
+  </si>
+  <si>
+    <t>0.0006,0.0004,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0030,0.9984,0.0022</t>
+  </si>
+  <si>
+    <t>0.0001,0.5700,0.9959,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0016,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0008,0.9961,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0093,0.9985,0.0015</t>
+  </si>
+  <si>
+    <t>0.0193,0.0003,0.9748,0.0012</t>
+  </si>
+  <si>
+    <t>0.1583,0.0005,0.8902,0.0004</t>
+  </si>
+  <si>
+    <t>0.9554,0.0007,0.0314,0.0003</t>
+  </si>
+  <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.5939,0.0005,0.3829,0.0045</t>
-  </si>
-  <si>
-    <t>0.0083,0.0013,0.9920,0.0005</t>
-  </si>
-  <si>
-    <t>0.0729,0.0043,0.9429,0.0001</t>
-  </si>
-  <si>
-    <t>0.0176,0.0006,0.9860,0.0003</t>
-  </si>
-  <si>
-    <t>0.9273,0.0010,0.0779,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9991,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0071,0.9898,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.9983,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1860,0.0002,0.8634,0.0005</t>
-  </si>
-  <si>
-    <t>0.0021,0.0015,0.9964,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0096,0.0002,0.9874,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.2175,0.0004,0.8214,0.0010</t>
-  </si>
-  <si>
-    <t>0.0294,0.0001,0.9795,0.0007</t>
-  </si>
-  <si>
-    <t>0.5484,0.3883,0.0085,0.0013</t>
-  </si>
-  <si>
-    <t>0.0873,0.0179,0.8771,0.0008</t>
-  </si>
-  <si>
-    <t>0.0016,0.0059,0.9969,0.0108</t>
-  </si>
-  <si>
-    <t>0.0030,0.9905,0.0100,0.0003</t>
-  </si>
-  <si>
-    <t>0.6375,0.0286,0.2085,0.0027</t>
-  </si>
-  <si>
-    <t>0.9488,0.0413,0.0041,0.0012</t>
-  </si>
-  <si>
-    <t>0.4852,0.5763,0.0029,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.9933,0.0128,0.0002</t>
-  </si>
-  <si>
-    <t>0.0161,0.2470,0.5500,0.0070</t>
-  </si>
-  <si>
-    <t>0.0278,0.0020,0.9294,0.0117</t>
-  </si>
-  <si>
-    <t>0.0200,0.0044,0.9666,0.0007</t>
-  </si>
-  <si>
-    <t>0.0018,0.0000,0.9975,0.0002</t>
-  </si>
-  <si>
-    <t>0.0026,0.0158,0.9929,0.0001</t>
-  </si>
-  <si>
-    <t>0.0034,0.9827,0.0124,0.0016</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9990,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.7357,0.0001,0.9890</t>
-  </si>
-  <si>
-    <t>0.0001,0.9962,0.0005,0.0281</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.0100,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0008,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0043,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0003,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0042,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.9895,0.0096,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9890,0.0091,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0032,0.9994,0.0019</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0021,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9957,0.0054,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9910,0.8999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0005,0.9857,0.0399</t>
-  </si>
-  <si>
-    <t>0.0000,0.6988,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0014</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.7839,0.0005,0.3139,0.0002</t>
-  </si>
-  <si>
-    <t>0.0057,0.0040,0.9942,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0052,0.9997,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.9504,0.9064,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9149,0.9713,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0111,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9915,0.9917,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0001,0.0002,0.9988</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0020,0.0002,0.0124,0.9952</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.0005,0.9997</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0002,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.9877,0.7728,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9895,0.9580,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8522,0.9951,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.3117,0.8667,0.0086</t>
-  </si>
-  <si>
-    <t>0.0000,0.9793,0.9856,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9441,0.9612,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0025,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9842,0.0226,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0049,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.9997,0.0005</t>
-  </si>
-  <si>
-    <t>0.9620,0.0021,0.0094,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0059,0.9914,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.0012,0.9974,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3137,0.7512,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.2839,0.0845,0.3439,0.0037</t>
-  </si>
-  <si>
-    <t>0.8579,0.0005,0.1679,0.0006</t>
-  </si>
-  <si>
-    <t>0.0661,0.5033,0.1678,0.0072</t>
-  </si>
-  <si>
-    <t>0.0677,0.0338,0.8263,0.0116</t>
-  </si>
-  <si>
-    <t>0.0063,0.0004,0.0677,0.9562</t>
-  </si>
-  <si>
-    <t>0.0001,0.9990,0.0157,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0000,0.0418</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9617,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9982,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.3882,0.5927,0.0081,0.0001</t>
-  </si>
-  <si>
-    <t>0.1599,0.8273,0.0087,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0016,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.2279,0.9961,0.0002</t>
-  </si>
-  <si>
-    <t>0.0016,0.4019,0.9815,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0041,0.9942,0.0006</t>
-  </si>
-  <si>
-    <t>0.0008,0.0003,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.9286,0.0041,0.0394,0.0009</t>
-  </si>
-  <si>
-    <t>0.9628,0.0005,0.0306,0.0006</t>
-  </si>
-  <si>
-    <t>0.0023,0.0003,0.9974,0.0002</t>
-  </si>
-  <si>
-    <t>0.7708,0.0015,0.2270,0.0017</t>
-  </si>
-  <si>
-    <t>0.0101,0.0002,0.0001,0.9974</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.0000,0.9925,0.9627,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0161,0.9784,0.0004,0.0052</t>
-  </si>
-  <si>
-    <t>0.9941,0.0023,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.8520,0.2031,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.6932,0.0012,0.0009,0.2778</t>
-  </si>
-  <si>
-    <t>0.0013,0.0040,0.9961,0.0035</t>
-  </si>
-  <si>
-    <t>0.9212,0.0004,0.0256,0.0172</t>
-  </si>
-  <si>
-    <t>0.9943,0.0015,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.0079,0.9853,0.0034,0.0013</t>
-  </si>
-  <si>
-    <t>0.9492,0.0136,0.0168,0.0023</t>
-  </si>
-  <si>
-    <t>0.9857,0.0009,0.0088,0.0005</t>
-  </si>
-  <si>
-    <t>0.1501,0.6565,0.0355,0.0052</t>
-  </si>
-  <si>
-    <t>0.4030,0.0767,0.2743,0.0005</t>
-  </si>
-  <si>
-    <t>0.8399,0.1341,0.0061,0.0013</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9948,0.0044,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9870,0.0108,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9532,0.0452,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.6805,0.3483,0.0044,0.0000</t>
-  </si>
-  <si>
-    <t>0.7125,0.3653,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.8365,0.2139,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9409,0.0971,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0012,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0011,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9942,0.0048,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9373,0.0288,0.0206,0.0019</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0056,0.1016,0.9847,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0809,0.9982,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.0057,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0000,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9989,0.0005</t>
-  </si>
-  <si>
-    <t>0.0055,0.0011,0.9926,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0014,0.9981,0.0002</t>
-  </si>
-  <si>
-    <t>0.0036,0.0019,0.9929,0.0012</t>
-  </si>
-  <si>
-    <t>0.0067,0.0012,0.9916,0.0001</t>
-  </si>
-  <si>
-    <t>0.0101,0.0242,0.9737,0.0007</t>
-  </si>
-  <si>
-    <t>0.0137,0.0030,0.9834,0.0008</t>
-  </si>
-  <si>
-    <t>0.0175,0.0084,0.9635,0.0037</t>
-  </si>
-  <si>
-    <t>0.1458,0.0096,0.8219,0.0011</t>
-  </si>
-  <si>
-    <t>0.0571,0.9473,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.0289,0.9799,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0336,0.9735,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.5586,0.6216,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.1711,0.8868,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.2520,0.5963,0.0162,0.0193</t>
-  </si>
-  <si>
-    <t>0.9938,0.0002,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.8764,0.0035,0.0507,0.0098</t>
-  </si>
-  <si>
-    <t>0.0090,0.0033,0.9815,0.0016</t>
-  </si>
-  <si>
-    <t>0.0447,0.0022,0.9465,0.0031</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9997,0.0015</t>
-  </si>
-  <si>
-    <t>0.0020,0.0483,0.9901,0.0006</t>
-  </si>
-  <si>
-    <t>0.0010,0.0115,0.9953,0.0008</t>
-  </si>
-  <si>
-    <t>0.0027,0.0025,0.9926,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0885,0.9987,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9745,0.0417,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0008,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0016,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0107,0.1036,0.9506,0.0011</t>
-  </si>
-  <si>
-    <t>0.7230,0.0067,0.2218,0.0079</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0010,0.9987,0.0015</t>
-  </si>
-  <si>
-    <t>0.0005,0.0139,0.9978,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0009,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0024,0.9939,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0032,0.9985,0.0218</t>
-  </si>
-  <si>
-    <t>0.0226,0.0009,0.9700,0.0030</t>
-  </si>
-  <si>
-    <t>0.0037,0.0005,0.9948,0.0004</t>
-  </si>
-  <si>
-    <t>0.9738,0.0029,0.0050,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0060,0.0016,0.9866,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0089,0.9982,0.0004</t>
-  </si>
-  <si>
-    <t>0.0032,0.0045,0.9910,0.0016</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.0005,0.9955,0.0007</t>
-  </si>
-  <si>
-    <t>0.0816,0.0098,0.8664,0.0035</t>
-  </si>
-  <si>
-    <t>0.0284,0.0025,0.9341,0.0153</t>
-  </si>
-  <si>
-    <t>0.9741,0.0003,0.0045,0.0121</t>
-  </si>
-  <si>
-    <t>0.0001,0.0100,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0042,0.0005,0.0004,0.9982</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.8433,0.0015,0.0027,0.0676</t>
+    <t>0.9784,0.0389,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9888,0.0130,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0018,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0007,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0168,0.9947,0.0005</t>
+  </si>
+  <si>
+    <t>0.0011,0.0072,0.9959,0.0006</t>
+  </si>
+  <si>
+    <t>0.0015,0.0001,0.9978,0.0005</t>
+  </si>
+  <si>
+    <t>0.0030,0.0004,0.9175,0.0812</t>
+  </si>
+  <si>
+    <t>0.1237,0.0161,0.7235,0.0121</t>
+  </si>
+  <si>
+    <t>0.0621,0.0009,0.9219,0.0039</t>
+  </si>
+  <si>
+    <t>0.9794,0.0007,0.0025,0.0072</t>
+  </si>
+  <si>
+    <t>0.0001,0.0057,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0019,0.0010,0.0003,0.9988</t>
+  </si>
+  <si>
+    <t>0.6203,0.0026,0.0055,0.2364</t>
   </si>
 </sst>
 </file>
@@ -1896,7 +1890,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1910,7 +1904,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1924,7 +1918,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1935,10 +1929,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1952,7 +1946,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1966,7 +1960,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1980,7 +1974,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1994,7 +1988,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2008,7 +2002,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2022,7 +2016,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2036,7 +2030,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2050,7 +2044,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2064,7 +2058,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2078,7 +2072,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2092,7 +2086,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2106,7 +2100,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2120,7 +2114,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2134,7 +2128,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2148,7 +2142,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2162,7 +2156,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2176,7 +2170,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2190,7 +2184,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2201,10 +2195,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2218,7 +2212,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2232,7 +2226,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2246,7 +2240,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2260,7 +2254,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2274,7 +2268,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2288,7 +2282,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2302,7 +2296,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2313,10 +2307,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2330,7 +2324,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2341,10 +2335,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2358,7 +2352,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2372,7 +2366,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2386,7 +2380,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2397,10 +2391,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2411,10 +2405,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2428,7 +2422,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2442,7 +2436,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2456,7 +2450,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2470,7 +2464,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2484,7 +2478,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2498,7 +2492,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2509,10 +2503,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2526,7 +2520,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2540,7 +2534,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2554,7 +2548,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2568,7 +2562,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2582,7 +2576,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2596,7 +2590,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2610,7 +2604,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2624,7 +2618,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2845,7 +2839,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
         <v>331</v>
@@ -2859,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
         <v>332</v>
@@ -3027,7 +3021,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
         <v>344</v>
@@ -3142,7 +3136,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3156,7 +3150,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3170,7 +3164,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3184,7 +3178,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3212,7 +3206,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3226,7 +3220,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3240,7 +3234,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>356</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3254,7 +3248,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3268,7 +3262,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>357</v>
+        <v>275</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3282,7 +3276,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3296,7 +3290,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3310,7 +3304,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3324,7 +3318,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3338,7 +3332,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3352,7 +3346,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3366,7 +3360,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3380,7 +3374,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3394,7 +3388,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3408,7 +3402,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3422,7 +3416,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3436,7 +3430,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3450,7 +3444,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3464,7 +3458,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3478,7 +3472,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3489,10 +3483,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3506,7 +3500,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3517,10 +3511,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3531,10 +3525,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3548,7 +3542,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3562,7 +3556,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3576,7 +3570,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3590,7 +3584,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3604,7 +3598,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3618,7 +3612,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3632,7 +3626,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3646,7 +3640,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3660,7 +3654,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>318</v>
+        <v>379</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3688,7 +3682,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>269</v>
+        <v>381</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3702,7 +3696,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3716,7 +3710,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3730,7 +3724,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3744,7 +3738,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3758,7 +3752,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3769,10 +3763,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3786,7 +3780,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3800,7 +3794,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3814,7 +3808,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3828,7 +3822,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3839,10 +3833,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3856,7 +3850,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3867,10 +3861,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3884,7 +3878,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3898,7 +3892,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>339</v>
+        <v>396</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3912,7 +3906,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3926,7 +3920,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>396</v>
+        <v>343</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3940,7 +3934,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3954,7 +3948,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>398</v>
+        <v>352</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4021,7 +4015,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>403</v>
@@ -4038,7 +4032,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4178,7 +4172,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>354</v>
+        <v>413</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4192,7 +4186,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>353</v>
+        <v>414</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4206,7 +4200,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4220,7 +4214,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4234,7 +4228,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4248,7 +4242,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4262,7 +4256,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4276,7 +4270,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4290,7 +4284,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4301,10 +4295,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4315,10 +4309,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4332,7 +4326,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4346,7 +4340,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4360,7 +4354,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4374,7 +4368,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4388,7 +4382,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4402,7 +4396,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4416,7 +4410,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4430,7 +4424,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4444,7 +4438,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4458,7 +4452,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4472,7 +4466,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4486,7 +4480,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4500,7 +4494,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4514,7 +4508,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4528,7 +4522,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4542,7 +4536,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4556,7 +4550,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4570,7 +4564,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4584,7 +4578,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4598,7 +4592,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4612,7 +4606,7 @@
         <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4626,7 +4620,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4640,7 +4634,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4654,7 +4648,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4668,7 +4662,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4679,10 +4673,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4696,7 +4690,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4707,10 +4701,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4724,7 +4718,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4738,7 +4732,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4752,7 +4746,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4766,7 +4760,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4780,7 +4774,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4794,7 +4788,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4808,7 +4802,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4822,7 +4816,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4836,7 +4830,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4850,7 +4844,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4864,7 +4858,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4878,7 +4872,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4892,7 +4886,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4906,7 +4900,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4920,7 +4914,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>464</v>
+        <v>322</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4948,7 +4942,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5029,7 +5023,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
         <v>471</v>
@@ -5158,7 +5152,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>353</v>
+        <v>271</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5214,7 +5208,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5256,7 +5250,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>354</v>
+        <v>275</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5424,7 +5418,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>496</v>
+        <v>396</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5438,7 +5432,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>497</v>
+        <v>396</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5452,7 +5446,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
